--- a/outputs/monitor_xlsx/20260325.xlsx
+++ b/outputs/monitor_xlsx/20260325.xlsx
@@ -544,10 +544,6 @@
           <t>+2.54%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.35%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+2.61%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-1.41%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+3.08%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+0.21%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+1.21%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-6.01%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-1.03%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>374.75億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-380.02億</t>
@@ -811,7 +774,6 @@
           <t>11.58億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>29.57億</t>
@@ -822,8 +784,6 @@
           <t>147.84億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.19%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>123.55%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>517.76億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>7331口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10063口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-57.35億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>4.89億</t>
@@ -1020,10 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2185,6 +2128,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>655</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>170</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-54</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-79</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" t="n">
+        <v>280</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1349</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-8969</v>
+      </c>
+      <c r="N19" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2325</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-252</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1867</v>
+      </c>
+      <c r="H20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2042</v>
+      </c>
+      <c r="J20" t="n">
+        <v>75</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2858</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11614</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-106311</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260325.xlsx
+++ b/outputs/monitor_xlsx/20260325.xlsx
@@ -544,6 +544,10 @@
           <t>+2.54%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>312.74</t>
+          <t>324.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.35%</t>
-        </is>
-      </c>
+          <t>+3.88%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +596,10 @@
           <t>+2.61%</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +622,10 @@
           <t>-1.41%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -624,14 +640,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4534.8$</t>
+          <t>4549.8$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3.08%</t>
-        </is>
-      </c>
+          <t>+3.42%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -654,6 +674,10 @@
           <t>+0.21%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -676,6 +700,10 @@
           <t>+1.21%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +726,10 @@
           <t>-6.01%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -712,14 +744,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>91.4$</t>
+          <t>90.32$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-1.03%</t>
-        </is>
-      </c>
+          <t>-2.20%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -737,24 +773,25 @@
           <t>374.75億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-380.02億</t>
+          <t>-154.53億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1900.12億</t>
+          <t>-772.66億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-374.34億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-7486.71億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -774,16 +811,19 @@
           <t>11.58億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.57億</t>
+          <t>25.34億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>147.84億</t>
-        </is>
-      </c>
+          <t>126.69億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -798,14 +838,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>141.19%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>123.55%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -823,6 +867,11 @@
           <t>517.76億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,11 +889,15 @@
           <t>7331口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10063口</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -862,6 +915,7 @@
           <t>-57.35億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>4.89億</t>
@@ -874,12 +928,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-14.16億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-283.19億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -926,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-380.02億</t>
+          <t>-154.53億</t>
         </is>
       </c>
     </row>
@@ -938,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1900.12億</t>
+          <t>-772.66億</t>
         </is>
       </c>
     </row>
@@ -950,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-374.34億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -962,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-7486.71億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -974,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29.57億</t>
+          <t>25.34億</t>
         </is>
       </c>
     </row>
@@ -986,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>147.84億</t>
+          <t>126.69億</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-14.16億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-283.19億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1105,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1122,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1201,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1289,12 +1340,7 @@
       <c r="N4" t="n">
         <v>-4536987</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1349,12 +1395,7 @@
       <c r="N5" t="n">
         <v>-78852</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1409,12 +1450,7 @@
       <c r="N6" t="n">
         <v>-649385</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1469,12 +1505,7 @@
       <c r="N7" t="n">
         <v>-6483113</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1483,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1497,44 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>-1.31</v>
+        <v>1685</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9.77</v>
       </c>
       <c r="F8" t="n">
-        <v>204010</v>
+        <v>6912</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-56510</v>
+        <v>-393</v>
       </c>
       <c r="H8" t="n">
-        <v>-170619</v>
+        <v>-491</v>
       </c>
       <c r="I8" t="n">
-        <v>-2755</v>
+        <v>194</v>
       </c>
       <c r="J8" t="n">
-        <v>42989</v>
+        <v>610</v>
       </c>
       <c r="K8" t="n">
-        <v>3146</v>
+        <v>171</v>
       </c>
       <c r="L8" t="n">
-        <v>135058</v>
+        <v>3107</v>
       </c>
       <c r="M8" t="n">
-        <v>524296</v>
+        <v>8864</v>
       </c>
       <c r="N8" t="n">
-        <v>-1125000</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140162</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1543,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1557,44 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2845</v>
+        <v>1625</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.96</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>3332</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>601</v>
+        <v>2325</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-252</v>
       </c>
       <c r="H9" t="n">
-        <v>-704</v>
+        <v>-1615</v>
       </c>
       <c r="I9" t="n">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="J9" t="n">
-        <v>217</v>
+        <v>1964</v>
       </c>
       <c r="K9" t="n">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>1966</v>
+        <v>2858</v>
       </c>
       <c r="M9" t="n">
-        <v>7894</v>
+        <v>12220</v>
       </c>
       <c r="N9" t="n">
-        <v>-89580</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106311</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1603,12 +1624,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1617,44 +1638,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2125</v>
+        <v>2845</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>9.82</v>
+        <v>5.96</v>
       </c>
       <c r="F10" t="n">
-        <v>2312</v>
+        <v>3332</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>223</v>
+        <v>601</v>
       </c>
       <c r="H10" t="n">
-        <v>-778</v>
+        <v>-704</v>
       </c>
       <c r="I10" t="n">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="J10" t="n">
-        <v>936</v>
+        <v>217</v>
       </c>
       <c r="K10" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L10" t="n">
-        <v>4273</v>
+        <v>1966</v>
       </c>
       <c r="M10" t="n">
-        <v>16580</v>
+        <v>7894</v>
       </c>
       <c r="N10" t="n">
-        <v>-19518</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89580</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1663,55 +1679,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1540</v>
+        <v>2125</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="F11" t="n">
-        <v>214</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>-18</v>
+        <v>2312</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>223</v>
       </c>
       <c r="H11" t="n">
-        <v>197</v>
+        <v>-778</v>
+      </c>
+      <c r="I11" t="n">
+        <v>57</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>936</v>
       </c>
       <c r="K11" t="n">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="L11" t="n">
-        <v>-20</v>
+        <v>4273</v>
       </c>
       <c r="M11" t="n">
-        <v>-309</v>
+        <v>16580</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19518</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1720,58 +1734,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>425.5</v>
+        <v>8450</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>9.949999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="F12" t="n">
-        <v>15554</v>
+        <v>655</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3132</v>
+        <v>86</v>
       </c>
       <c r="H12" t="n">
-        <v>1022</v>
+        <v>84</v>
       </c>
       <c r="I12" t="n">
-        <v>1440</v>
+        <v>-54</v>
       </c>
       <c r="J12" t="n">
-        <v>1246</v>
+        <v>-25</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>1115</v>
+        <v>280</v>
       </c>
       <c r="M12" t="n">
-        <v>287</v>
+        <v>1069</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8969</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1780,58 +1789,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1685</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.77</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>6912</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-393</v>
+        <v>-18</v>
       </c>
       <c r="H13" t="n">
-        <v>-491</v>
-      </c>
-      <c r="I13" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J13" t="n">
-        <v>610</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>3107</v>
+        <v>-20</v>
       </c>
       <c r="M13" t="n">
-        <v>8864</v>
+        <v>-309</v>
       </c>
       <c r="N13" t="n">
-        <v>-140162</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1840,12 +1841,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1854,44 +1855,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>898</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7.03</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1015</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>-94</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>3132</v>
       </c>
       <c r="H14" t="n">
-        <v>97</v>
+        <v>1022</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>1440</v>
       </c>
       <c r="J14" t="n">
-        <v>70</v>
+        <v>1246</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>225</v>
       </c>
       <c r="L14" t="n">
-        <v>-12</v>
+        <v>1115</v>
       </c>
       <c r="M14" t="n">
-        <v>-571</v>
+        <v>287</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1914,13 +1910,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>955</v>
+        <v>974</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>9.9</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>8091</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-139</v>
@@ -1946,12 +1942,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1960,280 +1951,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>251</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>7.04</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>3331</v>
+        <v>904</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>250</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>867</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-3</v>
+        <v>268</v>
       </c>
       <c r="J16" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="L16" t="n">
-        <v>6188</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>26365</v>
+        <v>-224</v>
       </c>
       <c r="N16" t="n">
-        <v>-59054</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>-9.58</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24025</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2470</v>
-      </c>
-      <c r="J17" t="n">
-        <v>200</v>
-      </c>
-      <c r="K17" t="n">
-        <v>614</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7037</v>
-      </c>
-      <c r="M17" t="n">
-        <v>31163</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-145262</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>-8.25</v>
-      </c>
-      <c r="F18" t="n">
-        <v>19998</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>-1512</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6710</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7793</v>
-      </c>
-      <c r="M18" t="n">
-        <v>31364</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-99396</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>8450</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>655</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="G19" t="n">
-        <v>170</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-54</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-79</v>
-      </c>
-      <c r="J19" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" t="n">
-        <v>280</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1349</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-8969</v>
-      </c>
-      <c r="N19" t="n">
-        <v>37.62</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1625</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2325</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>-252</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1867</v>
-      </c>
-      <c r="H20" t="n">
-        <v>78</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2042</v>
-      </c>
-      <c r="J20" t="n">
-        <v>75</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2858</v>
-      </c>
-      <c r="L20" t="n">
-        <v>11614</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-106311</v>
-      </c>
-      <c r="N20" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260325.xlsx
+++ b/outputs/monitor_xlsx/20260325.xlsx
@@ -544,10 +544,6 @@
           <t>+2.54%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+3.88%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+2.61%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>-1.41%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+3.42%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>+0.21%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+1.21%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-6.01%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-2.20%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>374.75億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-154.53億</t>
@@ -811,7 +774,6 @@
           <t>11.58億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>25.34億</t>
@@ -822,8 +784,6 @@
           <t>126.69億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>123.55%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>517.76億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>7331口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>10063口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-57.35億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>4.89億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="E17" t="n">
+        <v>789</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8034</v>
+      </c>
+      <c r="L17" t="n">
+        <v>41500</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22137</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.93</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260325.xlsx
+++ b/outputs/monitor_xlsx/20260325.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>76.2</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2.42</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>94344</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-2975</v>
       </c>
       <c r="H4" t="n">
-        <v>-230030</v>
+        <v>-233005</v>
       </c>
       <c r="I4" t="n">
         <v>-3670</v>
       </c>
       <c r="J4" t="n">
-        <v>3800</v>
+        <v>130</v>
       </c>
       <c r="K4" t="n">
         <v>15052</v>
@@ -1279,11 +1278,14 @@
         <v>12887</v>
       </c>
       <c r="M4" t="n">
-        <v>54099</v>
+        <v>66986</v>
       </c>
       <c r="N4" t="n">
         <v>-4536987</v>
       </c>
+      <c r="O4" t="n">
+        <v>-0.88</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>926</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5.11</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2917</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>830</v>
       </c>
       <c r="H5" t="n">
-        <v>-700</v>
+        <v>130</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="K5" t="n">
         <v>36</v>
@@ -1334,11 +1336,14 @@
         <v>2651</v>
       </c>
       <c r="M5" t="n">
-        <v>11585</v>
+        <v>14236</v>
       </c>
       <c r="N5" t="n">
         <v>-78852</v>
       </c>
+      <c r="O5" t="n">
+        <v>-1.34</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1550</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>16571</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>6440</v>
       </c>
       <c r="H6" t="n">
-        <v>3042</v>
+        <v>9481</v>
       </c>
       <c r="I6" t="n">
         <v>197</v>
       </c>
       <c r="J6" t="n">
-        <v>42</v>
+        <v>239</v>
       </c>
       <c r="K6" t="n">
         <v>526</v>
@@ -1389,11 +1394,14 @@
         <v>6118</v>
       </c>
       <c r="M6" t="n">
-        <v>21508</v>
+        <v>27626</v>
       </c>
       <c r="N6" t="n">
         <v>-649385</v>
       </c>
+      <c r="O6" t="n">
+        <v>11.61</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1845</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>1.93</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>46664</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>979</v>
       </c>
       <c r="H7" t="n">
-        <v>-50042</v>
+        <v>-49064</v>
       </c>
       <c r="I7" t="n">
         <v>265</v>
       </c>
       <c r="J7" t="n">
-        <v>-1576</v>
+        <v>-1311</v>
       </c>
       <c r="K7" t="n">
         <v>544</v>
@@ -1444,11 +1452,14 @@
         <v>26399</v>
       </c>
       <c r="M7" t="n">
-        <v>104973</v>
+        <v>131372</v>
       </c>
       <c r="N7" t="n">
         <v>-6483113</v>
       </c>
+      <c r="O7" t="n">
+        <v>-2.12</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1685</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>9.77</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>6912</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>-393</v>
       </c>
       <c r="H8" t="n">
-        <v>-491</v>
+        <v>-884</v>
       </c>
       <c r="I8" t="n">
         <v>194</v>
       </c>
       <c r="J8" t="n">
-        <v>610</v>
+        <v>804</v>
       </c>
       <c r="K8" t="n">
         <v>171</v>
@@ -1499,11 +1510,14 @@
         <v>3107</v>
       </c>
       <c r="M8" t="n">
-        <v>8864</v>
+        <v>11971</v>
       </c>
       <c r="N8" t="n">
         <v>-140162</v>
       </c>
+      <c r="O8" t="n">
+        <v>14.12</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1625</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>2325</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-252</v>
       </c>
       <c r="H9" t="n">
-        <v>-1615</v>
+        <v>-1867</v>
       </c>
       <c r="I9" t="n">
         <v>78</v>
       </c>
       <c r="J9" t="n">
-        <v>1964</v>
+        <v>2042</v>
       </c>
       <c r="K9" t="n">
         <v>75</v>
@@ -1554,11 +1568,14 @@
         <v>2858</v>
       </c>
       <c r="M9" t="n">
-        <v>12220</v>
+        <v>15078</v>
       </c>
       <c r="N9" t="n">
         <v>-106311</v>
       </c>
+      <c r="O9" t="n">
+        <v>11.78</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2845</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>5.96</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>3332</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>601</v>
       </c>
       <c r="H10" t="n">
-        <v>-704</v>
+        <v>-103</v>
       </c>
       <c r="I10" t="n">
         <v>197</v>
       </c>
       <c r="J10" t="n">
-        <v>217</v>
+        <v>414</v>
       </c>
       <c r="K10" t="n">
         <v>127</v>
@@ -1609,11 +1626,14 @@
         <v>1966</v>
       </c>
       <c r="M10" t="n">
-        <v>7894</v>
+        <v>9860</v>
       </c>
       <c r="N10" t="n">
         <v>-89580</v>
       </c>
+      <c r="O10" t="n">
+        <v>12.03</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2125</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>9.82</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>2312</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>223</v>
       </c>
       <c r="H11" t="n">
-        <v>-778</v>
+        <v>-555</v>
       </c>
       <c r="I11" t="n">
         <v>57</v>
       </c>
       <c r="J11" t="n">
-        <v>936</v>
+        <v>993</v>
       </c>
       <c r="K11" t="n">
         <v>129</v>
@@ -1664,11 +1684,14 @@
         <v>4273</v>
       </c>
       <c r="M11" t="n">
-        <v>16580</v>
+        <v>20853</v>
       </c>
       <c r="N11" t="n">
         <v>-19518</v>
       </c>
+      <c r="O11" t="n">
+        <v>9.960000000000001</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>8450</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>3.17</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>655</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>86</v>
       </c>
       <c r="H12" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="I12" t="n">
         <v>-54</v>
       </c>
       <c r="J12" t="n">
-        <v>-25</v>
+        <v>-79</v>
       </c>
       <c r="K12" t="n">
         <v>20</v>
@@ -1719,11 +1742,14 @@
         <v>280</v>
       </c>
       <c r="M12" t="n">
-        <v>1069</v>
+        <v>1349</v>
       </c>
       <c r="N12" t="n">
         <v>-8969</v>
       </c>
+      <c r="O12" t="n">
+        <v>37.62</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,20 +1772,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-18</v>
       </c>
       <c r="H13" t="n">
-        <v>197</v>
+        <v>179</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>8</v>
@@ -1771,11 +1800,14 @@
         <v>-20</v>
       </c>
       <c r="M13" t="n">
-        <v>-309</v>
+        <v>-329</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1798,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>3132</v>
       </c>
       <c r="H14" t="n">
-        <v>1022</v>
+        <v>4154</v>
       </c>
       <c r="I14" t="n">
         <v>1440</v>
       </c>
       <c r="J14" t="n">
-        <v>1246</v>
+        <v>2686</v>
       </c>
       <c r="K14" t="n">
         <v>225</v>
@@ -1826,11 +1858,14 @@
         <v>1115</v>
       </c>
       <c r="M14" t="n">
-        <v>287</v>
+        <v>1402</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1853,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>-139</v>
       </c>
       <c r="H15" t="n">
-        <v>-2828</v>
+        <v>-2967</v>
       </c>
       <c r="I15" t="n">
         <v>1188</v>
       </c>
       <c r="J15" t="n">
-        <v>3757</v>
+        <v>4945</v>
       </c>
       <c r="K15" t="n">
         <v>-29</v>
@@ -1881,11 +1916,14 @@
         <v>-2</v>
       </c>
       <c r="M15" t="n">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>268</v>
+        <v>277</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-6</v>
@@ -1933,11 +1974,14 @@
         <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>-224</v>
+        <v>-181</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>348.5</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>9.94</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>789</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>-5</v>
       </c>
-      <c r="G17" t="n">
-        <v>-172</v>
-      </c>
       <c r="H17" t="n">
+        <v>-238</v>
+      </c>
+      <c r="I17" t="n">
         <v>-2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>23</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>33</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8034</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>41500</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22137</v>
       </c>
-      <c r="N17" t="n">
-        <v>10.93</v>
+      <c r="O17" t="n">
+        <v>8.84</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260325.xlsx
+++ b/outputs/monitor_xlsx/20260325.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>8.84</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1620</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6144</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-843</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4279</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-168</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-728</v>
+      </c>
+      <c r="K18" t="n">
+        <v>186</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6309</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30633</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400976</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>506</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5286</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2310</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6045</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-44</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2036</v>
+      </c>
+      <c r="K19" t="n">
+        <v>704</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31656</v>
+      </c>
+      <c r="M19" t="n">
+        <v>164838</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393882</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>540</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11030</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>1653</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2240</v>
+      </c>
+      <c r="I20" t="n">
+        <v>510</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1462</v>
+      </c>
+      <c r="K20" t="n">
+        <v>47</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9657</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50979</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161014</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
